--- a/docs/pension_data_combined_2026-09-22.xlsx
+++ b/docs/pension_data_combined_2026-09-22.xlsx
@@ -1281,6 +1281,9 @@
       <c r="C51" t="n">
         <v>2.2398</v>
       </c>
+      <c r="D51" t="n">
+        <v>360160169</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1296,6 +1299,9 @@
       <c r="C52" t="n">
         <v>2.246</v>
       </c>
+      <c r="D52" t="n">
+        <v>438816366.8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1310,6 +1316,9 @@
       </c>
       <c r="C53" t="n">
         <v>1.9926</v>
+      </c>
+      <c r="D53" t="n">
+        <v>401001926.2</v>
       </c>
     </row>
     <row r="54">
